--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Mistral-Small-3.2-24B-Instruct-2506/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Mistral-Small-3.2-24B-Instruct-2506/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.8349514563106796</v>
+        <v>0.8777777777777778</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.6830985915492958</v>
+        <v>0.6690140845070423</v>
       </c>
       <c r="D2">
-        <v>0.3435114503816794</v>
+        <v>0.373015873015873</v>
       </c>
       <c r="E2">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
